--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349362</v>
+        <v>133349748</v>
       </c>
       <c r="B3" t="n">
-        <v>57879</v>
+        <v>58332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349748</v>
+        <v>133349484</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349484</v>
+        <v>133349362</v>
       </c>
       <c r="B5" t="n">
-        <v>58641</v>
+        <v>57879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349748</v>
+        <v>133349484</v>
       </c>
       <c r="B3" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349484</v>
+        <v>133349362</v>
       </c>
       <c r="B3" t="n">
-        <v>58641</v>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B5" t="n">
-        <v>57879</v>
+        <v>58641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,32 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133350526</v>
+        <v>133350119</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350119</v>
+        <v>133350526</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349748</v>
+        <v>133349362</v>
       </c>
       <c r="B3" t="n">
-        <v>58332</v>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B5" t="n">
-        <v>57879</v>
+        <v>58641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -1135,32 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133350119</v>
+        <v>133350526</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350526</v>
+        <v>133350119</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -1135,32 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133350526</v>
+        <v>133350119</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350119</v>
+        <v>133350526</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349748</v>
+        <v>133349484</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B5" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B3" t="n">
-        <v>57879</v>
+        <v>58641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133349362</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>57879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B3" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B4" t="n">
-        <v>57879</v>
+        <v>58641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349748</v>
+        <v>133349362</v>
       </c>
       <c r="B5" t="n">
-        <v>58332</v>
+        <v>57879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133350419</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>133349748</v>
       </c>
       <c r="B3" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133349362</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B5" t="n">
-        <v>57879</v>
+        <v>58648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,32 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133350119</v>
+        <v>133350526</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350526</v>
+        <v>133350119</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1368,7 @@
         <v>133349574</v>
       </c>
       <c r="B8" t="n">
-        <v>58502</v>
+        <v>58509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133350419</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349748</v>
+        <v>133349362</v>
       </c>
       <c r="B3" t="n">
-        <v>58339</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B5" t="n">
-        <v>58648</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
         <v>133350526</v>
       </c>
       <c r="B6" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>133350119</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>133349574</v>
       </c>
       <c r="B8" t="n">
-        <v>58509</v>
+        <v>58519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349362</v>
+        <v>133349748</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>58349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133349362</v>
       </c>
       <c r="B4" t="n">
-        <v>58658</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349748</v>
+        <v>133349484</v>
       </c>
       <c r="B5" t="n">
-        <v>58349</v>
+        <v>58658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349748</v>
+        <v>133349362</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349362</v>
+        <v>133349484</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349484</v>
+        <v>133349748</v>
       </c>
       <c r="B5" t="n">
-        <v>58658</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133350419</v>
+        <v>133349362</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>upptäckter (2)</t>
+          <t>20/4 - 29/4 upptäckter 8 (15)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133349362</v>
+        <v>133350119</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20/4 - 29/4 upptäckter 8 (15)</t>
+          <t>1/5 upptäckter 1 (2)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133349484</v>
+        <v>133350526</v>
       </c>
       <c r="B4" t="n">
-        <v>58658</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+          <t>25/4 - 5/5 upptäckter 29 (74)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133349748</v>
+        <v>133349574</v>
       </c>
       <c r="B5" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>21/4 - 6/5</t>
+          <t>30/4 uppräckter 1 (2)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133350526</v>
+        <v>133349748</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>25/4 - 5/5 upptäckter 29 (74)</t>
+          <t>21/4 - 6/5</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133350119</v>
+        <v>133350419</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1/5 upptäckter 1 (2)</t>
+          <t>upptäckter (2)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133349574</v>
+        <v>133350567</v>
       </c>
       <c r="B8" t="n">
-        <v>58519</v>
+        <v>58131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>103023</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>30/4 uppräckter 1 (2)</t>
+          <t>22/4 - 6/5 upptäckter 33 (470)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,6 +1477,236 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133349200</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Berget Väst, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>334899</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6386850</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>22/4 - 29/4 upptäckter 7 (7)</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133349484</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Berget Väst, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334899</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6386850</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>21/4 - 6/5 upptäckter 375 (689)</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61167-2024 artfynd.xlsx
+++ b/artfynd/A 61167-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133350119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133350526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349574</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133350419</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133350567</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,8 +1752,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349484</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>